--- a/Mimikara N3.xlsx
+++ b/Mimikara N3.xlsx
@@ -1372,27 +1372,7 @@
     <t>うつる</t>
   </si>
   <si>
-    <r>
-      <t>ch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ụ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <charset val="134"/>
-      </rPr>
-      <t>p</t>
-    </r>
+    <t>được chụp / hiện lên ảnh</t>
   </si>
   <si>
     <t>写す</t>
@@ -7261,7 +7241,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7444,12 +7424,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -7934,7 +7908,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7966,6 +7940,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10652,7 +10627,7 @@
       <c r="C147" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="D147" s="10" t="s">
+      <c r="D147" s="11" t="s">
         <v>434</v>
       </c>
       <c r="E147" s="7"/>
